--- a/test-artifacts/media-reports/broken-media.xlsx
+++ b/test-artifacts/media-reports/broken-media.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -397,83 +399,819 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H35"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
+      <c r="A1" s="1" t="str">
         <v>browserId</v>
       </c>
-      <c r="B1" t="str">
+      <c r="B1" s="1" t="str">
         <v>parentPage</v>
       </c>
-      <c r="C1" t="str">
+      <c r="C1" s="1" t="str">
         <v>fullMediaUrl</v>
       </c>
-      <c r="D1" t="str">
+      <c r="D1" s="1" t="str">
         <v>type</v>
       </c>
-      <c r="E1" t="str">
+      <c r="E1" s="1" t="str">
         <v>src</v>
       </c>
-      <c r="F1" t="str">
+      <c r="F1" s="1" t="str">
         <v>status</v>
       </c>
-      <c r="G1" t="str">
+      <c r="G1" s="1" t="str">
         <v>ok</v>
       </c>
-      <c r="H1" t="str">
+      <c r="H1" s="1" t="str">
         <v>error</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>B1-W1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/academics/</v>
-      </c>
-      <c r="C2" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/academics/wp-content/uploads/2025/04/my-geneseo.png</v>
-      </c>
-      <c r="D2" t="str">
-        <v>image</v>
-      </c>
-      <c r="E2" t="str">
-        <v>/wp-content/uploads/2025/04/my-geneseo.png</v>
-      </c>
-      <c r="F2">
-        <v>404</v>
-      </c>
-      <c r="G2" t="b">
+      <c r="A2" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B2" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C2" s="1" t="str">
+        <v>https://www.geneseo.edu/about/themes/custom/geneseo_bootstrap5/images/geneseo-logo-simple.png</v>
+      </c>
+      <c r="D2" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E2" s="1" t="str">
+        <v>/themes/custom/geneseo_bootstrap5/images/geneseo-logo-simple.png</v>
+      </c>
+      <c r="F2" s="1">
+        <v>404</v>
+      </c>
+      <c r="G2" s="1" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>B1-W1</v>
-      </c>
-      <c r="B3" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/admissions/</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://dev-suny-geneseo.pantheonsite.io/admissions/wp-content/uploads/2025/04/my-geneseo.png</v>
-      </c>
-      <c r="D3" t="str">
-        <v>image</v>
-      </c>
-      <c r="E3" t="str">
-        <v>/wp-content/uploads/2025/04/my-geneseo.png</v>
-      </c>
-      <c r="F3">
-        <v>404</v>
-      </c>
-      <c r="G3" t="b">
+      <c r="A3" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B3" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C3" s="1" t="str">
+        <v>https://www.geneseo.edu/about/themes/custom/geneseo_bootstrap5/images/my-geneseo.png</v>
+      </c>
+      <c r="D3" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E3" s="1" t="str">
+        <v>/themes/custom/geneseo_bootstrap5/images/my-geneseo.png</v>
+      </c>
+      <c r="F3" s="1">
+        <v>404</v>
+      </c>
+      <c r="G3" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B4" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C4" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/campus/sturges-hall.jpg</v>
+      </c>
+      <c r="D4" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E4" s="1" t="str">
+        <v>/sites/default/files/images/campus/sturges-hall.jpg</v>
+      </c>
+      <c r="F4" s="1">
+        <v>404</v>
+      </c>
+      <c r="G4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B5" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C5" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/pictures/medium/main-street-fountain-medium.jpg</v>
+      </c>
+      <c r="D5" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E5" s="1" t="str">
+        <v>/sites/default/files/pictures/medium/main-street-fountain-medium.jpg</v>
+      </c>
+      <c r="F5" s="1">
+        <v>404</v>
+      </c>
+      <c r="G5" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B6" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C6" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/campus/students-walking-fall-2018-clock-outside.jpg</v>
+      </c>
+      <c r="D6" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E6" s="1" t="str">
+        <v>/sites/default/files/images/campus/students-walking-fall-2018-clock-outside.jpg</v>
+      </c>
+      <c r="F6" s="1">
+        <v>404</v>
+      </c>
+      <c r="G6" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B7" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C7" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/students/girls-smiling-first-knight-2017.jpg</v>
+      </c>
+      <c r="D7" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E7" s="1" t="str">
+        <v>/sites/default/files/images/students/girls-smiling-first-knight-2017.jpg</v>
+      </c>
+      <c r="F7" s="1">
+        <v>404</v>
+      </c>
+      <c r="G7" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B8" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C8" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/students/students-in-chemistry-lab.jpg</v>
+      </c>
+      <c r="D8" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E8" s="1" t="str">
+        <v>/sites/default/files/images/students/students-in-chemistry-lab.jpg</v>
+      </c>
+      <c r="F8" s="1">
+        <v>404</v>
+      </c>
+      <c r="G8" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B9" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C9" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/students/students-spanish-club-hugging-square.jpg</v>
+      </c>
+      <c r="D9" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <v>/sites/default/files/images/students/students-spanish-club-hugging-square.jpg</v>
+      </c>
+      <c r="F9" s="1">
+        <v>404</v>
+      </c>
+      <c r="G9" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B10" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C10" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/students/students-studying-library-square.jpg</v>
+      </c>
+      <c r="D10" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E10" s="1" t="str">
+        <v>/sites/default/files/images/students/students-studying-library-square.jpg</v>
+      </c>
+      <c r="F10" s="1">
+        <v>404</v>
+      </c>
+      <c r="G10" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B11" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C11" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/classes-and-learning/jeff-over-teaching-geology-outside-square.jpg</v>
+      </c>
+      <c r="D11" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E11" s="1" t="str">
+        <v>/sites/default/files/images/classes-and-learning/jeff-over-teaching-geology-outside-square.jpg</v>
+      </c>
+      <c r="F11" s="1">
+        <v>404</v>
+      </c>
+      <c r="G11" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B12" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C12" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/campus/integrated-science-center-outside-fall-square.jpg</v>
+      </c>
+      <c r="D12" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E12" s="1" t="str">
+        <v>/sites/default/files/images/campus/integrated-science-center-outside-fall-square.jpg</v>
+      </c>
+      <c r="F12" s="1">
+        <v>404</v>
+      </c>
+      <c r="G12" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B13" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C13" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/students/female-physics-student-equipment.jpg</v>
+      </c>
+      <c r="D13" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <v>/sites/default/files/images/students/female-physics-student-equipment.jpg</v>
+      </c>
+      <c r="F13" s="1">
+        <v>404</v>
+      </c>
+      <c r="G13" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B14" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C14" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A1894.jpg?itok=F282_aFp</v>
+      </c>
+      <c r="D14" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E14" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A1894.jpg?itok=F282_aFp</v>
+      </c>
+      <c r="F14" s="1">
+        <v>404</v>
+      </c>
+      <c r="G14" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B15" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C15" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A1944.jpg?itok=BnuRlyB3</v>
+      </c>
+      <c r="D15" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E15" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A1944.jpg?itok=BnuRlyB3</v>
+      </c>
+      <c r="F15" s="1">
+        <v>404</v>
+      </c>
+      <c r="G15" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B16" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C16" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A2548.jpg?itok=DCNC207L</v>
+      </c>
+      <c r="D16" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E16" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A2548.jpg?itok=DCNC207L</v>
+      </c>
+      <c r="F16" s="1">
+        <v>404</v>
+      </c>
+      <c r="G16" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B17" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C17" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A5644.jpg?itok=E_WMPNZd</v>
+      </c>
+      <c r="D17" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E17" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A5644.jpg?itok=E_WMPNZd</v>
+      </c>
+      <c r="F17" s="1">
+        <v>404</v>
+      </c>
+      <c r="G17" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B18" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C18" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A7018.jpg?itok=9N856RE7</v>
+      </c>
+      <c r="D18" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E18" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A7018.jpg?itok=9N856RE7</v>
+      </c>
+      <c r="F18" s="1">
+        <v>404</v>
+      </c>
+      <c r="G18" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B19" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C19" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A9615.jpg?itok=tyWUvzWD</v>
+      </c>
+      <c r="D19" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E19" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A9615.jpg?itok=tyWUvzWD</v>
+      </c>
+      <c r="F19" s="1">
+        <v>404</v>
+      </c>
+      <c r="G19" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B20" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C20" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A9785.jpg?itok=XDvDkS-D</v>
+      </c>
+      <c r="D20" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E20" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/4J7A9785.jpg?itok=XDvDkS-D</v>
+      </c>
+      <c r="F20" s="1">
+        <v>404</v>
+      </c>
+      <c r="G20" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B21" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C21" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/7D0A9534.jpg?itok=sWeuerUv</v>
+      </c>
+      <c r="D21" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/7D0A9534.jpg?itok=sWeuerUv</v>
+      </c>
+      <c r="F21" s="1">
+        <v>404</v>
+      </c>
+      <c r="G21" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B22" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C22" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/20151114_171_XC-Men.jpg?itok=bAVrUSxb</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E22" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/20151114_171_XC-Men.jpg?itok=bAVrUSxb</v>
+      </c>
+      <c r="F22" s="1">
+        <v>404</v>
+      </c>
+      <c r="G22" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B23" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C23" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/20151114_312_XC-Women.jpg?itok=NGdfSiAt</v>
+      </c>
+      <c r="D23" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/20151114_312_XC-Women.jpg?itok=NGdfSiAt</v>
+      </c>
+      <c r="F23" s="1">
+        <v>404</v>
+      </c>
+      <c r="G23" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B24" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C24" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R0971.jpg?itok=jAcwTs1E</v>
+      </c>
+      <c r="D24" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E24" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R0971.jpg?itok=jAcwTs1E</v>
+      </c>
+      <c r="F24" s="1">
+        <v>404</v>
+      </c>
+      <c r="G24" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B25" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C25" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R3108.jpg?itok=5rFz2gx6</v>
+      </c>
+      <c r="D25" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E25" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R3108.jpg?itok=5rFz2gx6</v>
+      </c>
+      <c r="F25" s="1">
+        <v>404</v>
+      </c>
+      <c r="G25" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B26" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C26" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R4481.jpg?itok=qnj0nF9w</v>
+      </c>
+      <c r="D26" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R4481.jpg?itok=qnj0nF9w</v>
+      </c>
+      <c r="F26" s="1">
+        <v>404</v>
+      </c>
+      <c r="G26" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B27" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C27" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R5248.jpg?itok=HPYMxwT4</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R5248.jpg?itok=HPYMxwT4</v>
+      </c>
+      <c r="F27" s="1">
+        <v>404</v>
+      </c>
+      <c r="G27" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B28" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C28" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R7551.jpg?itok=EIZeq6gF</v>
+      </c>
+      <c r="D28" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E28" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R7551.jpg?itok=EIZeq6gF</v>
+      </c>
+      <c r="F28" s="1">
+        <v>404</v>
+      </c>
+      <c r="G28" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B29" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C29" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R8001.jpg?itok=N7Y7XvUQ</v>
+      </c>
+      <c r="D29" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E29" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R8001.jpg?itok=N7Y7XvUQ</v>
+      </c>
+      <c r="F29" s="1">
+        <v>404</v>
+      </c>
+      <c r="G29" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B30" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C30" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R8899.jpg?itok=99OCiht7</v>
+      </c>
+      <c r="D30" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <v>/sites/default/files/styles/bootstrap_m_1x/public/images/CQ2R8899.jpg?itok=99OCiht7</v>
+      </c>
+      <c r="F30" s="1">
+        <v>404</v>
+      </c>
+      <c r="G30" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B31" s="1" t="str">
+        <v>https://www.geneseo.edu/about</v>
+      </c>
+      <c r="C31" s="1" t="str">
+        <v>https://www.geneseo.edu/about/sites/default/files/images/students/students-biology-geography-oak-research-field.jpg</v>
+      </c>
+      <c r="D31" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <v>/sites/default/files/images/students/students-biology-geography-oak-research-field.jpg</v>
+      </c>
+      <c r="F31" s="1">
+        <v>404</v>
+      </c>
+      <c r="G31" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B32" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply?utm_source=postcard&amp;utm_medium=print&amp;utm_campaign=apply_early_action_0823</v>
+      </c>
+      <c r="C32" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply/themes/custom/geneseo_bootstrap5/images/geneseo-logo-simple.png</v>
+      </c>
+      <c r="D32" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <v>/themes/custom/geneseo_bootstrap5/images/geneseo-logo-simple.png</v>
+      </c>
+      <c r="F32" s="1">
+        <v>404</v>
+      </c>
+      <c r="G32" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B33" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply?utm_source=postcard&amp;utm_medium=print&amp;utm_campaign=apply_early_action_0823</v>
+      </c>
+      <c r="C33" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply/themes/custom/geneseo_bootstrap5/images/my-geneseo.png</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E33" s="1" t="str">
+        <v>/themes/custom/geneseo_bootstrap5/images/my-geneseo.png</v>
+      </c>
+      <c r="F33" s="1">
+        <v>404</v>
+      </c>
+      <c r="G33" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B34" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply?utm_source=postcard&amp;utm_medium=print&amp;utm_campaign=apply_early_action_0823</v>
+      </c>
+      <c r="C34" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply/sites/default/files/images/campus/sturges-hall-square.jpg</v>
+      </c>
+      <c r="D34" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <v>/sites/default/files/images/campus/sturges-hall-square.jpg</v>
+      </c>
+      <c r="F34" s="1">
+        <v>404</v>
+      </c>
+      <c r="G34" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="str">
+        <v>B1-W1</v>
+      </c>
+      <c r="B35" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply?utm_source=postcard&amp;utm_medium=print&amp;utm_campaign=apply_early_action_0823</v>
+      </c>
+      <c r="C35" s="1" t="str">
+        <v>https://www.geneseo.edu/admissions/apply/sites/default/files/images/classes-and-learning/trading-room-students-square.jpg</v>
+      </c>
+      <c r="D35" s="1" t="str">
+        <v>image</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <v>/sites/default/files/images/classes-and-learning/trading-room-students-square.jpg</v>
+      </c>
+      <c r="F35" s="1">
+        <v>404</v>
+      </c>
+      <c r="G35" s="1" t="b">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H35"/>
   </ignoredErrors>
 </worksheet>
 </file>